--- a/data/2. OUTPUT/3. FILTRADO/Licitaciones_Filtradas_20250813.xlsx
+++ b/data/2. OUTPUT/3. FILTRADO/Licitaciones_Filtradas_20250813.xlsx
@@ -509,4 +509,748 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C6BE542E5FD1F8449FAB2AFE9595F7C2" ma:contentTypeVersion="35" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="95a25fb6fd0be9d04bd8b7d8c4571d77">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="f25b715f-fa92-46b3-80c4-70202bf57239" xmlns:ns3="a0e75e46-6eaf-4811-90a9-43566dd9aec2" xmlns:ns4="9a1a681d-ea20-4416-922c-eca11cc2463a" xmlns:ns5="http://schemas.microsoft.com/sharepoint/v3/fields" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5d7e2a98a8196fd26160c74a574bfa16" ns1:_="" ns2:_="" ns3:_="" ns4:_="" ns5:_="">
+    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
+    <xsd:import namespace="f25b715f-fa92-46b3-80c4-70202bf57239"/>
+    <xsd:import namespace="a0e75e46-6eaf-4811-90a9-43566dd9aec2"/>
+    <xsd:import namespace="9a1a681d-ea20-4416-922c-eca11cc2463a"/>
+    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3/fields"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:ArchivedGADA" minOccurs="0"/>
+                <xsd:element ref="ns3:Pa_x00ed_s" minOccurs="0"/>
+                <xsd:element ref="ns3:n3ya" minOccurs="0"/>
+                <xsd:element ref="ns3:A_x00f1_o_x0020_de_x0020_comienzo" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns4:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns4:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns4:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyProperties" minOccurs="0"/>
+                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyUIAction" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns5:_DCDateCreated" minOccurs="0"/>
+                <xsd:element ref="ns3:L_x00ed_neadenegocio" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceBillingMetadata" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="29" nillable="true" ma:displayName="Propiedades de la Directiva de cumplimiento unificado" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="30" nillable="true" ma:displayName="Acción de IU de la Directiva de cumplimiento unificado" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f25b715f-fa92-46b3-80c4-70202bf57239" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="ArchivedGADA" ma:index="8" nillable="true" ma:displayName="ArchivedGADA" ma:default="" ma:format="Dropdown" ma:internalName="ArchivedGADA">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Choice">
+          <xsd:enumeration value="Sí"/>
+          <xsd:enumeration value="No"/>
+          <xsd:enumeration value="Retenido"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a0e75e46-6eaf-4811-90a9-43566dd9aec2" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="Pa_x00ed_s" ma:index="9" nillable="true" ma:displayName="País" ma:format="Dropdown" ma:internalName="Pa_x00ed_s">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Choice">
+          <xsd:enumeration value="Afghanistan"/>
+          <xsd:enumeration value="Albania"/>
+          <xsd:enumeration value="Algeria"/>
+          <xsd:enumeration value="Andorra"/>
+          <xsd:enumeration value="Angola"/>
+          <xsd:enumeration value="Antigua and Barbuda"/>
+          <xsd:enumeration value="Argentina"/>
+          <xsd:enumeration value="Armenia"/>
+          <xsd:enumeration value="Australia"/>
+          <xsd:enumeration value="Austria"/>
+          <xsd:enumeration value="Azerbaijan"/>
+          <xsd:enumeration value="The Bahamas"/>
+          <xsd:enumeration value="Bahrain"/>
+          <xsd:enumeration value="Bangladesh"/>
+          <xsd:enumeration value="Barbados"/>
+          <xsd:enumeration value="Belarus"/>
+          <xsd:enumeration value="Belgium"/>
+          <xsd:enumeration value="Belize"/>
+          <xsd:enumeration value="Benin"/>
+          <xsd:enumeration value="Bhutan"/>
+          <xsd:enumeration value="Bolivia"/>
+          <xsd:enumeration value="Bosnia and Herzegovina"/>
+          <xsd:enumeration value="Botswana"/>
+          <xsd:enumeration value="Brazil"/>
+          <xsd:enumeration value="Brunei"/>
+          <xsd:enumeration value="Bulgaria"/>
+          <xsd:enumeration value="Burkina Faso"/>
+          <xsd:enumeration value="Burundi"/>
+          <xsd:enumeration value="Cabo Verde"/>
+          <xsd:enumeration value="Cambodia"/>
+          <xsd:enumeration value="Cameroon"/>
+          <xsd:enumeration value="Canada"/>
+          <xsd:enumeration value="Central African Republic"/>
+          <xsd:enumeration value="Chad"/>
+          <xsd:enumeration value="Chile"/>
+          <xsd:enumeration value="China"/>
+          <xsd:enumeration value="Colombia"/>
+          <xsd:enumeration value="Comoros"/>
+          <xsd:enumeration value="Congo, Democratic Republic of the"/>
+          <xsd:enumeration value="Congo, Republic of the"/>
+          <xsd:enumeration value="Costa Rica"/>
+          <xsd:enumeration value="Côte d’Ivoire"/>
+          <xsd:enumeration value="Croatia"/>
+          <xsd:enumeration value="Cuba"/>
+          <xsd:enumeration value="Cyprus"/>
+          <xsd:enumeration value="Czech Republic"/>
+          <xsd:enumeration value="Denmark"/>
+          <xsd:enumeration value="Djibouti"/>
+          <xsd:enumeration value="Dominica"/>
+          <xsd:enumeration value="Dominican Republic"/>
+          <xsd:enumeration value="East Timor (Timor-Leste)"/>
+          <xsd:enumeration value="Ecuador"/>
+          <xsd:enumeration value="Egypt"/>
+          <xsd:enumeration value="El Salvador"/>
+          <xsd:enumeration value="Equatorial Guinea"/>
+          <xsd:enumeration value="Eritrea"/>
+          <xsd:enumeration value="Estonia"/>
+          <xsd:enumeration value="Eswatini"/>
+          <xsd:enumeration value="Ethiopia"/>
+          <xsd:enumeration value="Fiji"/>
+          <xsd:enumeration value="Finland"/>
+          <xsd:enumeration value="France"/>
+          <xsd:enumeration value="Gabon"/>
+          <xsd:enumeration value="The Gambia"/>
+          <xsd:enumeration value="Georgia"/>
+          <xsd:enumeration value="Germany"/>
+          <xsd:enumeration value="Ghana"/>
+          <xsd:enumeration value="Greece"/>
+          <xsd:enumeration value="Grenada"/>
+          <xsd:enumeration value="Guatemala"/>
+          <xsd:enumeration value="Guinea"/>
+          <xsd:enumeration value="Guinea-Bissau"/>
+          <xsd:enumeration value="Guyana"/>
+          <xsd:enumeration value="Haiti"/>
+          <xsd:enumeration value="Honduras"/>
+          <xsd:enumeration value="Hungary"/>
+          <xsd:enumeration value="Iceland"/>
+          <xsd:enumeration value="India"/>
+          <xsd:enumeration value="Indonesia"/>
+          <xsd:enumeration value="Iran"/>
+          <xsd:enumeration value="Iraq"/>
+          <xsd:enumeration value="Ireland"/>
+          <xsd:enumeration value="Israel"/>
+          <xsd:enumeration value="Italy"/>
+          <xsd:enumeration value="Jamaica"/>
+          <xsd:enumeration value="Japan"/>
+          <xsd:enumeration value="Jordan"/>
+          <xsd:enumeration value="Kazakhstan"/>
+          <xsd:enumeration value="Kenya"/>
+          <xsd:enumeration value="Kiribati"/>
+          <xsd:enumeration value="Korea, North"/>
+          <xsd:enumeration value="Korea, South"/>
+          <xsd:enumeration value="Kosovo"/>
+          <xsd:enumeration value="Kuwait"/>
+          <xsd:enumeration value="Kyrgyzstan"/>
+          <xsd:enumeration value="Laos"/>
+          <xsd:enumeration value="Latvia"/>
+          <xsd:enumeration value="Lebanon"/>
+          <xsd:enumeration value="Lesotho"/>
+          <xsd:enumeration value="Liberia"/>
+          <xsd:enumeration value="Libya"/>
+          <xsd:enumeration value="Liechtenstein"/>
+          <xsd:enumeration value="Lithuania"/>
+          <xsd:enumeration value="Luxembourg"/>
+          <xsd:enumeration value="Madagascar"/>
+          <xsd:enumeration value="Malawi"/>
+          <xsd:enumeration value="Malaysia"/>
+          <xsd:enumeration value="Maldives"/>
+          <xsd:enumeration value="Mali"/>
+          <xsd:enumeration value="Malta"/>
+          <xsd:enumeration value="Marshall Islands"/>
+          <xsd:enumeration value="Mauritania"/>
+          <xsd:enumeration value="Mauritius"/>
+          <xsd:enumeration value="Mexico"/>
+          <xsd:enumeration value="Micronesia, Federated States of"/>
+          <xsd:enumeration value="Moldova"/>
+          <xsd:enumeration value="Monaco"/>
+          <xsd:enumeration value="Mongolia"/>
+          <xsd:enumeration value="Montenegro"/>
+          <xsd:enumeration value="Morocco"/>
+          <xsd:enumeration value="Mozambique"/>
+          <xsd:enumeration value="Myanmar (Burma)"/>
+          <xsd:enumeration value="Namibia"/>
+          <xsd:enumeration value="Nauru"/>
+          <xsd:enumeration value="Nepal"/>
+          <xsd:enumeration value="Netherlands"/>
+          <xsd:enumeration value="New Zealand"/>
+          <xsd:enumeration value="Nicaragua"/>
+          <xsd:enumeration value="Niger"/>
+          <xsd:enumeration value="Nigeria"/>
+          <xsd:enumeration value="North Macedonia"/>
+          <xsd:enumeration value="Norway"/>
+          <xsd:enumeration value="Oman"/>
+          <xsd:enumeration value="Pakistan"/>
+          <xsd:enumeration value="Palau"/>
+          <xsd:enumeration value="Panama"/>
+          <xsd:enumeration value="Papua New Guinea"/>
+          <xsd:enumeration value="Paraguay"/>
+          <xsd:enumeration value="Peru"/>
+          <xsd:enumeration value="Philippines"/>
+          <xsd:enumeration value="Poland"/>
+          <xsd:enumeration value="Portugal"/>
+          <xsd:enumeration value="Qatar"/>
+          <xsd:enumeration value="Romania"/>
+          <xsd:enumeration value="Russia"/>
+          <xsd:enumeration value="Rwanda"/>
+          <xsd:enumeration value="Saint Kitts and Nevis"/>
+          <xsd:enumeration value="Saint Lucia"/>
+          <xsd:enumeration value="Saint Vincent and the Grenadines"/>
+          <xsd:enumeration value="Samoa"/>
+          <xsd:enumeration value="San Marino"/>
+          <xsd:enumeration value="Sao Tome and Principe"/>
+          <xsd:enumeration value="Saudi Arabia"/>
+          <xsd:enumeration value="Senegal"/>
+          <xsd:enumeration value="Serbia"/>
+          <xsd:enumeration value="Seychelles"/>
+          <xsd:enumeration value="Sierra Leone"/>
+          <xsd:enumeration value="Singapore"/>
+          <xsd:enumeration value="Slovakia"/>
+          <xsd:enumeration value="Slovenia"/>
+          <xsd:enumeration value="Solomon Islands"/>
+          <xsd:enumeration value="Somalia"/>
+          <xsd:enumeration value="South Africa"/>
+          <xsd:enumeration value="Spain"/>
+          <xsd:enumeration value="Sri Lanka"/>
+          <xsd:enumeration value="Sudan"/>
+          <xsd:enumeration value="Sudan, South"/>
+          <xsd:enumeration value="Suriname"/>
+          <xsd:enumeration value="Sweden"/>
+          <xsd:enumeration value="Switzerland"/>
+          <xsd:enumeration value="Syria"/>
+          <xsd:enumeration value="Taiwan"/>
+          <xsd:enumeration value="Tajikistan"/>
+          <xsd:enumeration value="Tanzania"/>
+          <xsd:enumeration value="Thailand"/>
+          <xsd:enumeration value="Togo"/>
+          <xsd:enumeration value="Tonga"/>
+          <xsd:enumeration value="Trinidad and Tobago"/>
+          <xsd:enumeration value="Tunisia"/>
+          <xsd:enumeration value="Turkey"/>
+          <xsd:enumeration value="Turkmenistan"/>
+          <xsd:enumeration value="Tuvalu"/>
+          <xsd:enumeration value="Uganda"/>
+          <xsd:enumeration value="Ukraine"/>
+          <xsd:enumeration value="United Arab Emirates"/>
+          <xsd:enumeration value="United Kingdom"/>
+          <xsd:enumeration value="United States"/>
+          <xsd:enumeration value="Uruguay"/>
+          <xsd:enumeration value="Uzbekistan"/>
+          <xsd:enumeration value="Vanuatu"/>
+          <xsd:enumeration value="Vatican City"/>
+          <xsd:enumeration value="Venezuela"/>
+          <xsd:enumeration value="Vietnam"/>
+          <xsd:enumeration value="Yemen"/>
+          <xsd:enumeration value="Zambia"/>
+          <xsd:enumeration value="Zimbabwe"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="n3ya" ma:index="10" nillable="true" ma:displayName="Responsable" ma:list="UserInfo" ma:internalName="n3ya">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:User">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="A_x00f1_o_x0020_de_x0020_comienzo" ma:index="11" nillable="true" ma:displayName="Año de comienzo" ma:format="Dropdown" ma:internalName="A_x00f1_o_x0020_de_x0020_comienzo">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Choice">
+          <xsd:enumeration value="1957"/>
+          <xsd:enumeration value="1958"/>
+          <xsd:enumeration value="1959"/>
+          <xsd:enumeration value="1960"/>
+          <xsd:enumeration value="1961"/>
+          <xsd:enumeration value="1962"/>
+          <xsd:enumeration value="1963"/>
+          <xsd:enumeration value="1964"/>
+          <xsd:enumeration value="1965"/>
+          <xsd:enumeration value="1966"/>
+          <xsd:enumeration value="1967"/>
+          <xsd:enumeration value="1968"/>
+          <xsd:enumeration value="1969"/>
+          <xsd:enumeration value="1970"/>
+          <xsd:enumeration value="1971"/>
+          <xsd:enumeration value="1972"/>
+          <xsd:enumeration value="1973"/>
+          <xsd:enumeration value="1974"/>
+          <xsd:enumeration value="1975"/>
+          <xsd:enumeration value="1976"/>
+          <xsd:enumeration value="1977"/>
+          <xsd:enumeration value="1978"/>
+          <xsd:enumeration value="1979"/>
+          <xsd:enumeration value="1980"/>
+          <xsd:enumeration value="1981"/>
+          <xsd:enumeration value="1982"/>
+          <xsd:enumeration value="1983"/>
+          <xsd:enumeration value="1984"/>
+          <xsd:enumeration value="1985"/>
+          <xsd:enumeration value="1986"/>
+          <xsd:enumeration value="1987"/>
+          <xsd:enumeration value="1988"/>
+          <xsd:enumeration value="1989"/>
+          <xsd:enumeration value="1990"/>
+          <xsd:enumeration value="1991"/>
+          <xsd:enumeration value="1992"/>
+          <xsd:enumeration value="1993"/>
+          <xsd:enumeration value="1994"/>
+          <xsd:enumeration value="1995"/>
+          <xsd:enumeration value="1996"/>
+          <xsd:enumeration value="1997"/>
+          <xsd:enumeration value="1998"/>
+          <xsd:enumeration value="1999"/>
+          <xsd:enumeration value="2000"/>
+          <xsd:enumeration value="2001"/>
+          <xsd:enumeration value="2002"/>
+          <xsd:enumeration value="2003"/>
+          <xsd:enumeration value="2004"/>
+          <xsd:enumeration value="2005"/>
+          <xsd:enumeration value="2006"/>
+          <xsd:enumeration value="2007"/>
+          <xsd:enumeration value="2008"/>
+          <xsd:enumeration value="2009"/>
+          <xsd:enumeration value="2010"/>
+          <xsd:enumeration value="2011"/>
+          <xsd:enumeration value="2012"/>
+          <xsd:enumeration value="2013"/>
+          <xsd:enumeration value="2014"/>
+          <xsd:enumeration value="2015"/>
+          <xsd:enumeration value="2016"/>
+          <xsd:enumeration value="2017"/>
+          <xsd:enumeration value="2018"/>
+          <xsd:enumeration value="2019"/>
+          <xsd:enumeration value="2020"/>
+          <xsd:enumeration value="2021"/>
+          <xsd:enumeration value="2022"/>
+          <xsd:enumeration value="2023"/>
+          <xsd:enumeration value="2024"/>
+          <xsd:enumeration value="2025"/>
+          <xsd:enumeration value="2026"/>
+          <xsd:enumeration value="2027"/>
+          <xsd:enumeration value="2028"/>
+          <xsd:enumeration value="2029"/>
+          <xsd:enumeration value="2030"/>
+          <xsd:enumeration value="2031"/>
+          <xsd:enumeration value="2032"/>
+          <xsd:enumeration value="2033"/>
+          <xsd:enumeration value="2034"/>
+          <xsd:enumeration value="2035"/>
+          <xsd:enumeration value="2036"/>
+          <xsd:enumeration value="2037"/>
+          <xsd:enumeration value="2038"/>
+          <xsd:enumeration value="2039"/>
+          <xsd:enumeration value="2040"/>
+          <xsd:enumeration value="2041"/>
+          <xsd:enumeration value="2042"/>
+          <xsd:enumeration value="2043"/>
+          <xsd:enumeration value="2044"/>
+          <xsd:enumeration value="2045"/>
+          <xsd:enumeration value="2046"/>
+          <xsd:enumeration value="2047"/>
+          <xsd:enumeration value="2048"/>
+          <xsd:enumeration value="2049"/>
+          <xsd:enumeration value="2050"/>
+          <xsd:enumeration value="2051"/>
+          <xsd:enumeration value="2052"/>
+          <xsd:enumeration value="2053"/>
+          <xsd:enumeration value="2054"/>
+          <xsd:enumeration value="2055"/>
+          <xsd:enumeration value="2056"/>
+          <xsd:enumeration value="2057"/>
+          <xsd:enumeration value="2058"/>
+          <xsd:enumeration value="2059"/>
+          <xsd:enumeration value="2060"/>
+          <xsd:enumeration value="2061"/>
+          <xsd:enumeration value="2062"/>
+          <xsd:enumeration value="2063"/>
+          <xsd:enumeration value="2064"/>
+          <xsd:enumeration value="2065"/>
+          <xsd:enumeration value="2066"/>
+          <xsd:enumeration value="2067"/>
+          <xsd:enumeration value="2068"/>
+          <xsd:enumeration value="2069"/>
+          <xsd:enumeration value="2070"/>
+          <xsd:enumeration value="2071"/>
+          <xsd:enumeration value="2072"/>
+          <xsd:enumeration value="2073"/>
+          <xsd:enumeration value="2074"/>
+          <xsd:enumeration value="2075"/>
+          <xsd:enumeration value="2076"/>
+          <xsd:enumeration value="2077"/>
+          <xsd:enumeration value="2078"/>
+          <xsd:enumeration value="2079"/>
+          <xsd:enumeration value="2080"/>
+          <xsd:enumeration value="2081"/>
+          <xsd:enumeration value="2082"/>
+          <xsd:enumeration value="2083"/>
+          <xsd:enumeration value="2084"/>
+          <xsd:enumeration value="2085"/>
+          <xsd:enumeration value="2086"/>
+          <xsd:enumeration value="2087"/>
+          <xsd:enumeration value="2088"/>
+          <xsd:enumeration value="2089"/>
+          <xsd:enumeration value="2090"/>
+          <xsd:enumeration value="2091"/>
+          <xsd:enumeration value="2092"/>
+          <xsd:enumeration value="2093"/>
+          <xsd:enumeration value="2094"/>
+          <xsd:enumeration value="2095"/>
+          <xsd:enumeration value="2096"/>
+          <xsd:enumeration value="2097"/>
+          <xsd:enumeration value="2098"/>
+          <xsd:enumeration value="2099"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="13" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="19" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="20" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="23" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="25" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="022c8e44-81e4-4e05-b6ee-54b8eab20e48" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="27" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="28" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="31" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="L_x00ed_neadenegocio" ma:index="33" nillable="true" ma:displayName="Línea de negocio" ma:format="Dropdown" ma:internalName="L_x00ed_neadenegocio">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Choice">
+          <xsd:enumeration value="ITS"/>
+          <xsd:enumeration value="Redes y Operadores"/>
+          <xsd:enumeration value="Seguridad e Integración"/>
+          <xsd:enumeration value="Ticketing y Recaudo"/>
+          <xsd:enumeration value="Consultoría Tecnológica"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="34" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9a1a681d-ea20-4416-922c-eca11cc2463a" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="21" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="22" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="26" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{369e2034-ca09-4801-97ac-bec56d307d66}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="9a1a681d-ea20-4416-922c-eca11cc2463a">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3/fields" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="_DCDateCreated" ma:index="32" nillable="true" ma:displayName="Fecha de creación" ma:description="Fecha en la que se creó el recurso" ma:format="DateTime" ma:internalName="_DCDateCreated">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:DateTime"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="022c8e44-81e4-4e05-b6ee-54b8eab20e48" ContentTypeId="0x0101" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <L_x00ed_neadenegocio xmlns="a0e75e46-6eaf-4811-90a9-43566dd9aec2" xsi:nil="true"/>
+    <TaxCatchAll xmlns="9a1a681d-ea20-4416-922c-eca11cc2463a" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Pa_x00ed_s xmlns="a0e75e46-6eaf-4811-90a9-43566dd9aec2" xsi:nil="true"/>
+    <n3ya xmlns="a0e75e46-6eaf-4811-90a9-43566dd9aec2">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </n3ya>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <A_x00f1_o_x0020_de_x0020_comienzo xmlns="a0e75e46-6eaf-4811-90a9-43566dd9aec2" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a0e75e46-6eaf-4811-90a9-43566dd9aec2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ArchivedGADA xmlns="f25b715f-fa92-46b3-80c4-70202bf57239" xsi:nil="true"/>
+    <_DCDateCreated xmlns="http://schemas.microsoft.com/sharepoint/v3/fields" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA5BF201-F187-4052-8D7B-64EB9E947AE9}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68BEE39E-9F4B-4C31-A1AC-274C347C8D73}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F48A5F8-1891-429C-AFF0-EF08F90A51B5}"/>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57DE0E44-6750-4708-9D81-EF07A8E8BA5B}"/>
 </file>